--- a/Experiment/analysis/SecondExp/RecallAnalysis/Weights_calibrated.xlsx
+++ b/Experiment/analysis/SecondExp/RecallAnalysis/Weights_calibrated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barak\Documents\GitHub\startegicMW_lite\Experiment\analysis\RecallAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\barak\Documents\GitHub\startegicMW_lite\Experiment\analysis\SecondExp\RecallAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3FAF37-227C-4DDC-A511-F75853682250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A688E590-534F-4C30-A045-62F876AFDE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -699,10 +699,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -716,10 +712,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -729,6 +721,10 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -769,14 +765,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4378474D-1CC4-4FD7-BD9C-0416E143AE67}" name="Calibrated_weights_v2__by_relation_name_" displayName="Calibrated_weights_v2__by_relation_name_" ref="A1:G1048576" tableType="queryTable" totalsRowShown="0" dataDxfId="7">
   <autoFilter ref="A1:G1048576" xr:uid="{4378474D-1CC4-4FD7-BD9C-0416E143AE67}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G66">
-    <sortCondition ref="D1:D1048576"/>
+    <sortCondition ref="A1:A1048576"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{213B6130-3CE6-4551-8121-63814AAC56EC}" uniqueName="1" name="id" queryTableFieldId="1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{8E130B0C-F755-4F4A-8E55-403AF19ACD06}" uniqueName="2" name="RelationName" queryTableFieldId="2" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{317A505A-D45F-48F6-A0FA-6B21B63C4F4B}" uniqueName="3" name="Weight" queryTableFieldId="3" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{0525565E-04C4-477E-81A8-09FA1B5CBADF}" uniqueName="4" name="Weight_Calibrated" queryTableFieldId="4" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{DB55D218-110E-40B7-B8AE-30CF76C56206}" uniqueName="5" name="Calibration_Justification" queryTableFieldId="5" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{213B6130-3CE6-4551-8121-63814AAC56EC}" uniqueName="1" name="id" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{8E130B0C-F755-4F4A-8E55-403AF19ACD06}" uniqueName="2" name="RelationName" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{317A505A-D45F-48F6-A0FA-6B21B63C4F4B}" uniqueName="3" name="Weight" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{0525565E-04C4-477E-81A8-09FA1B5CBADF}" uniqueName="4" name="Weight_Calibrated" queryTableFieldId="4" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{DB55D218-110E-40B7-B8AE-30CF76C56206}" uniqueName="5" name="Calibration_Justification" queryTableFieldId="5" dataDxfId="2"/>
     <tableColumn id="6" xr3:uid="{7275E246-BD5D-483B-94F2-B103E007595E}" uniqueName="6" name="RelationCount" queryTableFieldId="6" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{C5FB274B-2338-4D4D-AEE4-FDFFE5DBB6CA}" uniqueName="7" name="description" queryTableFieldId="7" dataDxfId="0"/>
   </tableColumns>
@@ -1074,12 +1070,12 @@
   <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33" style="5" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="28.77734375" style="4" customWidth="1"/>
     <col min="4" max="4" width="39.109375" style="4" customWidth="1"/>
-    <col min="5" max="5" width="55.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="39.5546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="55.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" customWidth="1"/>
+    <col min="7" max="7" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1107,227 +1103,233 @@
     </row>
     <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="3">
+        <v>213713</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="3">
+        <v>213713</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="3">
+        <v>26131</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="3">
+        <v>31596</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="3">
+        <v>66</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="3">
+        <v>768</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4">
         <v>1.9</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D8" s="4">
         <v>0.15</v>
       </c>
-      <c r="E2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="6">
-        <v>45801</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>60</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.9</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="E8" t="s">
         <v>160</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F8" s="3">
         <v>12430</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>198</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="6">
-        <v>94246</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>232</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="6">
-        <v>24784</v>
-      </c>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>3004</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.9</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="6">
-        <v>16544</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>227</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="6">
-        <v>5434</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="6">
-        <v>213713</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4">
         <v>1.7</v>
       </c>
       <c r="D9" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="3">
+        <v>9434</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="4">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F9" s="6">
-        <v>213713</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>3012</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1.7</v>
-      </c>
       <c r="D10" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1393</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>91</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" s="6">
-        <v>8642</v>
-      </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>3011</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1.7</v>
-      </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F11" s="6">
-        <v>8642</v>
-      </c>
-      <c r="G11" s="6"/>
+        <v>190</v>
+      </c>
+      <c r="F11" s="3">
+        <v>237</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
@@ -1345,10 +1347,10 @@
       <c r="E12" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3">
         <v>6518</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="3" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1368,772 +1370,772 @@
       <c r="E13" t="s">
         <v>170</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="3">
         <v>6518</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C14" s="4">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D14" s="4">
-        <v>1.05</v>
+        <v>0.15</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
-      </c>
-      <c r="F14" s="6">
-        <v>185194</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+      <c r="F14" s="3">
+        <v>45801</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C15" s="4">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="D15" s="4">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="E15" t="s">
-        <v>173</v>
-      </c>
-      <c r="F15" s="6">
-        <v>185189</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+      <c r="F15" s="3">
+        <v>828</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D16" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1236</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3783</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>3418</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C17" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4">
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="6">
-        <v>418</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F17" s="3">
+        <v>610</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C18" s="4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D18" s="4">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E18" t="s">
         <v>171</v>
       </c>
-      <c r="F18" s="6">
-        <v>768</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="F18" s="3">
+        <v>1236</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>3435</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="D19" s="4">
         <v>1.2</v>
       </c>
       <c r="E19" t="s">
-        <v>171</v>
-      </c>
-      <c r="F19" s="6">
-        <v>732</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+      <c r="F19" s="3">
+        <v>16250</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>3433</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4">
         <v>0.8</v>
       </c>
       <c r="D20" s="4">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F20" s="6">
-        <v>723</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2324</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C21" s="4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D21" s="4">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="E21" t="s">
-        <v>171</v>
-      </c>
-      <c r="F21" s="6">
-        <v>429</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2329</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>3443</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="4">
         <v>0.8</v>
       </c>
       <c r="D22" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>188</v>
+      </c>
+      <c r="F22" s="3">
+        <v>553</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>155</v>
+      </c>
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D23" s="4">
         <v>1.2</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>171</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F23" s="3">
         <v>429</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>197</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="3">
+        <v>185194</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>198</v>
+      </c>
+      <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="4">
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="3">
+        <v>94246</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>199</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="3">
+        <v>185189</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>200</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="4">
         <v>1.4</v>
       </c>
-      <c r="D23" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="E23" t="s">
-        <v>174</v>
-      </c>
-      <c r="F23" s="6">
-        <v>31596</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="4">
+      <c r="D27" s="4">
         <v>1.4</v>
       </c>
-      <c r="D24" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="E24" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" s="6">
-        <v>26131</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="E27" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="3">
+        <v>18933</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
         <v>204</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B28" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C28" s="4">
         <v>1.4</v>
       </c>
-      <c r="D25" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D28" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="E28" t="s">
         <v>176</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F28" s="3">
         <v>18933</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G28" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>200</v>
-      </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E26" t="s">
-        <v>177</v>
-      </c>
-      <c r="F26" s="6">
-        <v>18933</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>115</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>178</v>
-      </c>
-      <c r="F27" s="6">
-        <v>3783</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>3432</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E28" t="s">
+    <row r="29" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>227</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5434</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>232</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="4">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="3">
+        <v>24784</v>
+      </c>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>3004</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" s="3">
+        <v>16544</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>3011</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F32" s="3">
+        <v>8642</v>
+      </c>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>3012</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1.7</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" s="3">
+        <v>8642</v>
+      </c>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>3418</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E34" t="s">
         <v>171</v>
       </c>
-      <c r="F28" s="6">
-        <v>1457</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>3465</v>
-      </c>
-      <c r="B29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="6">
-        <v>1015</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="F34" s="3">
+        <v>418</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B30" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>179</v>
-      </c>
-      <c r="F30" s="6">
-        <v>828</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>3434</v>
-      </c>
-      <c r="B31" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="D31" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E31" t="s">
-        <v>180</v>
-      </c>
-      <c r="F31" s="6">
-        <v>792</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>128</v>
-      </c>
-      <c r="B32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="4">
-        <v>1</v>
-      </c>
-      <c r="D32" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>171</v>
-      </c>
-      <c r="F32" s="6">
-        <v>610</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>3455</v>
-      </c>
-      <c r="B33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>163</v>
-      </c>
-      <c r="F33" s="6">
-        <v>494</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <v>3459</v>
-      </c>
-      <c r="B34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D34" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="6">
-        <v>362</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>3458</v>
+        <v>3422</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C35" s="4">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="D35" s="4">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="E35" t="s">
-        <v>163</v>
-      </c>
-      <c r="F35" s="6">
-        <v>301</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>116</v>
+        <v>192</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1132</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>3454</v>
+        <v>3428</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C36" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D36" s="4">
         <v>1.3</v>
       </c>
       <c r="E36" t="s">
-        <v>163</v>
-      </c>
-      <c r="F36" s="6">
-        <v>241</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="F36" s="3">
+        <v>306</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>3453</v>
+        <v>3429</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C37" s="4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D37" s="4">
         <v>1.3</v>
       </c>
       <c r="E37" t="s">
-        <v>163</v>
-      </c>
-      <c r="F37" s="6">
-        <v>220</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1028</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>3449</v>
+        <v>3432</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C38" s="4">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="D38" s="4">
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F38" s="6">
-        <v>204</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1457</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>3473</v>
+        <v>3433</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="C39" s="4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D39" s="4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E39" t="s">
-        <v>164</v>
-      </c>
-      <c r="F39" s="6">
-        <v>93</v>
-      </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+      <c r="F39" s="3">
+        <v>723</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>3457</v>
+        <v>3434</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C40" s="4">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D40" s="4">
         <v>1.3</v>
       </c>
       <c r="E40" t="s">
-        <v>163</v>
-      </c>
-      <c r="F40" s="6">
-        <v>82</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="F40" s="3">
+        <v>792</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>3463</v>
+        <v>3435</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C41" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="3">
+        <v>732</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>3436</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="D42" s="4">
         <v>1.5</v>
       </c>
-      <c r="D41" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="E41" t="s">
-        <v>163</v>
-      </c>
-      <c r="F41" s="6">
-        <v>79</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
-        <v>3460</v>
-      </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D42" s="4">
-        <v>1.3</v>
-      </c>
       <c r="E42" t="s">
-        <v>163</v>
-      </c>
-      <c r="F42" s="6">
-        <v>78</v>
-      </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="F42" s="3">
+        <v>184</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>3456</v>
+        <v>3437</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C43" s="4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D43" s="4">
         <v>1.3</v>
       </c>
       <c r="E43" t="s">
-        <v>163</v>
-      </c>
-      <c r="F43" s="6">
-        <v>78</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="F43" s="3">
+        <v>416</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>3470</v>
+        <v>3438</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C44" s="4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D44" s="4">
         <v>1.3</v>
       </c>
       <c r="E44" t="s">
-        <v>163</v>
-      </c>
-      <c r="F44" s="6">
-        <v>72</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="F44" s="3">
+        <v>85</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>3472</v>
+        <v>3439</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C45" s="4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D45" s="4">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="E45" t="s">
-        <v>163</v>
-      </c>
-      <c r="F45" s="6">
-        <v>43</v>
-      </c>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+      <c r="F45" s="3">
+        <v>553</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>3471</v>
+        <v>3443</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C46" s="4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D46" s="4">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E46" t="s">
-        <v>163</v>
-      </c>
-      <c r="F46" s="6">
-        <v>24</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+      <c r="F46" s="3">
+        <v>429</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>3469</v>
+        <v>3449</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C47" s="4">
         <v>1.5</v>
@@ -2144,339 +2146,337 @@
       <c r="E47" t="s">
         <v>163</v>
       </c>
-      <c r="F47" s="6">
-        <v>16</v>
-      </c>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="F47" s="3">
+        <v>204</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>3466</v>
+        <v>3453</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C48" s="4">
         <v>1.5</v>
       </c>
       <c r="D48" s="4">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E48" t="s">
         <v>163</v>
       </c>
-      <c r="F48" s="6">
-        <v>12</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="F48" s="3">
+        <v>220</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>145</v>
+        <v>3454</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C49" s="4">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D49" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="3">
+        <v>241</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <v>3455</v>
+      </c>
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="4">
         <v>1.5</v>
       </c>
-      <c r="E49" t="s">
-        <v>181</v>
-      </c>
-      <c r="F49" s="6">
-        <v>16250</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
-        <v>3468</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="4">
-        <v>0.8</v>
-      </c>
       <c r="D50" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="E50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50" s="3">
+        <v>494</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <v>3456</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="4">
         <v>1.5</v>
-      </c>
-      <c r="E50" t="s">
-        <v>182</v>
-      </c>
-      <c r="F50" s="6">
-        <v>96</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
-        <v>3495</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" s="4">
-        <v>0.9</v>
       </c>
       <c r="D51" s="4">
         <v>1.6</v>
       </c>
       <c r="E51" t="s">
-        <v>183</v>
-      </c>
-      <c r="F51" s="6">
-        <v>2660</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F51" s="3">
+        <v>78</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>147</v>
+        <v>3457</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C52" s="4">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D52" s="4">
         <v>1.6</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
-      </c>
-      <c r="F52" s="6">
-        <v>2329</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F52" s="3">
+        <v>82</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>146</v>
+        <v>3458</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C53" s="4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D53" s="4">
         <v>1.6</v>
       </c>
       <c r="E53" t="s">
-        <v>185</v>
-      </c>
-      <c r="F53" s="6">
-        <v>2324</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>94</v>
+        <v>163</v>
+      </c>
+      <c r="F53" s="3">
+        <v>301</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>86</v>
+        <v>3459</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C54" s="4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D54" s="4">
         <v>1.6</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
-      </c>
-      <c r="F54" s="6">
-        <v>1393</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F54" s="3">
+        <v>362</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>3429</v>
+        <v>3460</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C55" s="4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D55" s="4">
         <v>1.6</v>
       </c>
       <c r="E55" t="s">
-        <v>187</v>
-      </c>
-      <c r="F55" s="6">
-        <v>1028</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F55" s="3">
+        <v>78</v>
+      </c>
+      <c r="G55" s="3"/>
+    </row>
+    <row r="56" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>154</v>
+        <v>3462</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C56" s="4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D56" s="4">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>188</v>
-      </c>
-      <c r="F56" s="6">
-        <v>553</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="F56" s="3">
+        <v>1744</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>3439</v>
+        <v>3463</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C57" s="4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D57" s="4">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E57" t="s">
-        <v>188</v>
-      </c>
-      <c r="F57" s="6">
-        <v>553</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F57" s="3">
+        <v>79</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>3437</v>
+        <v>3465</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C58" s="4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D58" s="4">
         <v>1.6</v>
       </c>
       <c r="E58" t="s">
-        <v>189</v>
-      </c>
-      <c r="F58" s="6">
-        <v>416</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>113</v>
+        <v>163</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1015</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>3428</v>
+        <v>3466</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C59" s="4">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D59" s="4">
         <v>1.6</v>
       </c>
       <c r="E59" t="s">
-        <v>189</v>
-      </c>
-      <c r="F59" s="6">
-        <v>306</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F59" s="3">
+        <v>12</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>91</v>
+        <v>3468</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C60" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D60" s="4">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="E60" t="s">
-        <v>190</v>
-      </c>
-      <c r="F60" s="6">
-        <v>237</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+      <c r="F60" s="3">
+        <v>96</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>3438</v>
+        <v>3469</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C61" s="4">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D61" s="4">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E61" t="s">
-        <v>189</v>
-      </c>
-      <c r="F61" s="6">
-        <v>85</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>123</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F61" s="3">
+        <v>16</v>
+      </c>
+      <c r="G61" s="3"/>
     </row>
     <row r="62" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>54</v>
+        <v>3470</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C62" s="4">
         <v>1.5</v>
@@ -2485,105 +2485,101 @@
         <v>1.6</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
-      </c>
-      <c r="F62" s="6">
-        <v>66</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+      <c r="F62" s="3">
+        <v>72</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>3422</v>
+        <v>3471</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C63" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="D63" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="E63" t="s">
+        <v>163</v>
+      </c>
+      <c r="F63" s="3">
+        <v>24</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>3472</v>
+      </c>
+      <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="E64" t="s">
+        <v>163</v>
+      </c>
+      <c r="F64" s="3">
+        <v>43</v>
+      </c>
+      <c r="G64" s="3"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>3473</v>
+      </c>
+      <c r="B65" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="D65" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="E65" t="s">
+        <v>164</v>
+      </c>
+      <c r="F65" s="3">
+        <v>93</v>
+      </c>
+      <c r="G65" s="3"/>
+    </row>
+    <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>3495</v>
+      </c>
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" s="4">
         <v>0.9</v>
       </c>
-      <c r="D63" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="E63" t="s">
-        <v>192</v>
-      </c>
-      <c r="F63" s="6">
-        <v>1132</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
-        <v>3436</v>
-      </c>
-      <c r="B64" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="D64" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="E64" t="s">
-        <v>193</v>
-      </c>
-      <c r="F64" s="6">
-        <v>184</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
-        <v>80</v>
-      </c>
-      <c r="B65" t="s">
-        <v>25</v>
-      </c>
-      <c r="C65" s="4">
-        <v>1.7</v>
-      </c>
-      <c r="D65" s="4">
-        <v>2</v>
-      </c>
-      <c r="E65" t="s">
-        <v>194</v>
-      </c>
-      <c r="F65" s="6">
-        <v>9434</v>
-      </c>
-      <c r="G65" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
-        <v>3462</v>
-      </c>
-      <c r="B66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C66" s="4">
-        <v>1.5</v>
-      </c>
       <c r="D66" s="4">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E66" t="s">
-        <v>195</v>
-      </c>
-      <c r="F66" s="6">
-        <v>1744</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>95</v>
+        <v>183</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2660</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
